--- a/src/test/resources/migration/excel/drom-transfer-sample.xlsx
+++ b/src/test/resources/migration/excel/drom-transfer-sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,6 +525,21 @@
       <c r="V1" t="inlineStr">
         <is>
           <t>Фото</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Может подойти</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Прочие поля</t>
         </is>
       </c>
     </row>
